--- a/fixtures/broken_impossible_port_codes.xlsx
+++ b/fixtures/broken_impossible_port_codes.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -437,6 +437,16 @@
           <t>base_rate_usd</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>validity_start</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>validity_end</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -457,6 +467,16 @@
       <c r="D2" t="n">
         <v>2100</v>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -477,6 +497,16 @@
       <c r="D3" t="n">
         <v>1850</v>
       </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -497,6 +527,16 @@
       <c r="D4" t="n">
         <v>2450</v>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -517,6 +557,16 @@
       <c r="D5" t="n">
         <v>1750</v>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -536,6 +586,16 @@
       </c>
       <c r="D6" t="n">
         <v>2200</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/fixtures/broken_impossible_port_codes.xlsx
+++ b/fixtures/broken_impossible_port_codes.xlsx
@@ -511,7 +511,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ZZZZZ</t>
+          <t>ZZ@ZZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -576,7 +576,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>QQQQQ</t>
+          <t>QQ@QQ</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
